--- a/ConsoleAppAccountingAd/AdAgency_Report.xlsx
+++ b/ConsoleAppAccountingAd/AdAgency_Report.xlsx
@@ -25,7 +25,7 @@
     <x:t>Фамилия клиента</x:t>
   </x:si>
   <x:si>
-    <x:t>Имя клиентиа</x:t>
+    <x:t>Имя клиента</x:t>
   </x:si>
   <x:si>
     <x:t>номер мобильного телефона</x:t>
@@ -88,6 +88,12 @@
     <x:t>банеры</x:t>
   </x:si>
   <x:si>
+    <x:t>YouTube</x:t>
+  </x:si>
+  <x:si>
+    <x:t>видеоролики</x:t>
+  </x:si>
+  <x:si>
     <x:t>Платформы</x:t>
   </x:si>
   <x:si>
@@ -113,6 +119,18 @@
   </x:si>
   <x:si>
     <x:t>Пожелания клиента</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Завершён</x:t>
+  </x:si>
+  <x:si>
+    <x:t>сделать банер с рекламой поярче</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ожидание</x:t>
+  </x:si>
+  <x:si>
+    <x:t>реклама в виде видеоигры межпланетной</x:t>
   </x:si>
   <x:si>
     <x:t>Заказы</x:t>
@@ -122,8 +140,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
   </x:numFmts>
   <x:fonts count="2">
     <x:font>
@@ -225,7 +244,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -241,8 +260,11 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="6">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -261,6 +283,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellXfs>
@@ -564,13 +590,13 @@
     <x:col min="1" max="1" width="2.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="27.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="17.567768" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.996339" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="28.567768" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="27.710625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.140625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="2.710625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="21.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.424911" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.567768" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="48.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="30.424911" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="12.853482" style="0" customWidth="1"/>
@@ -581,8 +607,8 @@
     <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="13.282054" style="0" customWidth="1"/>
     <x:col min="20" max="20" width="20.139196" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="6.710625" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="19.567768" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="10.710625" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="40.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:22">
@@ -595,7 +621,7 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="4"/>
       <x:c r="H1" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I1" s="4"/>
       <x:c r="J1" s="4"/>
@@ -603,7 +629,7 @@
       <x:c r="L1" s="4"/>
       <x:c r="M1" s="4"/>
       <x:c r="O1" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P1" s="4"/>
       <x:c r="Q1" s="4"/>
@@ -651,28 +677,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="P2" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q2" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R2" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S2" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="T2" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="U2" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="V2" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:22">
@@ -712,6 +738,30 @@
       <x:c r="M3" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="P3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q3" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R3" s="5">
+        <x:v>39490</x:v>
+      </x:c>
+      <x:c r="S3" s="5">
+        <x:v>46065</x:v>
+      </x:c>
+      <x:c r="T3" s="0">
+        <x:v>6575</x:v>
+      </x:c>
+      <x:c r="U3" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="V3" s="0" t="s">
+        <x:v>36</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:22">
       <x:c r="A4" s="0">
@@ -731,6 +781,48 @@
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>16</x:v>
+      </x:c>
+      <x:c r="H4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="J4" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="K4" s="0">
+        <x:v>228.51</x:v>
+      </x:c>
+      <x:c r="L4" s="0">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="M4" s="0" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O4" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="P4" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="R4" s="5">
+        <x:v>761475</x:v>
+      </x:c>
+      <x:c r="S4" s="5">
+        <x:v>768785</x:v>
+      </x:c>
+      <x:c r="T4" s="0">
+        <x:v>7310</x:v>
+      </x:c>
+      <x:c r="U4" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="V4" s="0" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ConsoleAppAccountingAd/AdAgency_Report.xlsx
+++ b/ConsoleAppAccountingAd/AdAgency_Report.xlsx
@@ -37,7 +37,7 @@
     <x:t>Клиенты</x:t>
   </x:si>
   <x:si>
-    <x:t>Леново</x:t>
+    <x:t>Починка</x:t>
   </x:si>
   <x:si>
     <x:t>Радкевич</x:t>
@@ -49,22 +49,7 @@
     <x:t>+375299825520</x:t>
   </x:si>
   <x:si>
-    <x:t>sapcoputers4391@gmail.com</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Илья и ты</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Егоров</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Илья</x:t>
-  </x:si>
-  <x:si>
-    <x:t>+375259752757</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Egorov@gmail.com</x:t>
+    <x:t>Sapcoputers4391@gmail.com</x:t>
   </x:si>
   <x:si>
     <x:t>Название платформы</x:t>
@@ -82,16 +67,10 @@
     <x:t>Доступность</x:t>
   </x:si>
   <x:si>
-    <x:t>Обьявления.бу</x:t>
-  </x:si>
-  <x:si>
-    <x:t>банеры</x:t>
-  </x:si>
-  <x:si>
     <x:t>YouTube</x:t>
   </x:si>
   <x:si>
-    <x:t>видеоролики</x:t>
+    <x:t>видеохостинг</x:t>
   </x:si>
   <x:si>
     <x:t>Платформы</x:t>
@@ -121,16 +100,10 @@
     <x:t>Пожелания клиента</x:t>
   </x:si>
   <x:si>
-    <x:t>Завершён</x:t>
-  </x:si>
-  <x:si>
-    <x:t>сделать банер с рекламой поярче</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ожидание</x:t>
-  </x:si>
-  <x:si>
-    <x:t>реклама в виде видеоигры межпланетной</x:t>
+    <x:t>Активен</x:t>
+  </x:si>
+  <x:si>
+    <x:t>нету</x:t>
   </x:si>
   <x:si>
     <x:t>Заказы</x:t>
@@ -584,7 +557,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V4"/>
+  <x:dimension ref="A1:V3"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="2.710625" style="0" customWidth="1"/>
@@ -592,11 +565,11 @@
     <x:col min="3" max="3" width="17.567768" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="12.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="28.567768" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="27.710625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27.853482" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="9.140625" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="2.710625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="21.139196" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="13.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.710625" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="48.567768" style="0" customWidth="1"/>
     <x:col min="12" max="12" width="30.424911" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="12.853482" style="0" customWidth="1"/>
@@ -607,8 +580,8 @@
     <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="13.282054" style="0" customWidth="1"/>
     <x:col min="20" max="20" width="20.139196" style="0" customWidth="1"/>
-    <x:col min="21" max="21" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="22" max="22" width="40.853482" style="0" customWidth="1"/>
+    <x:col min="21" max="21" width="8.567768" style="0" customWidth="1"/>
+    <x:col min="22" max="22" width="19.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:22">
@@ -621,7 +594,7 @@
       <x:c r="E1" s="3"/>
       <x:c r="F1" s="4"/>
       <x:c r="H1" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I1" s="4"/>
       <x:c r="J1" s="4"/>
@@ -629,7 +602,7 @@
       <x:c r="L1" s="4"/>
       <x:c r="M1" s="4"/>
       <x:c r="O1" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P1" s="4"/>
       <x:c r="Q1" s="4"/>
@@ -662,43 +635,43 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="J2" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="O2" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="M2" s="0" t="s">
+      <x:c r="P2" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="O2" s="0" t="s">
+      <x:c r="Q2" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="R2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="S2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="T2" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="U2" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="V2" s="0" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="R2" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="S2" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="T2" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="U2" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="V2" s="0" t="s">
-        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:22">
@@ -721,22 +694,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="H3" s="0">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="K3" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="L3" s="0">
-        <x:v>300</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="M3" s="0" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O3" s="0">
         <x:v>1</x:v>
@@ -745,84 +718,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="R3" s="5">
-        <x:v>39490</x:v>
+        <x:v>46141</x:v>
       </x:c>
       <x:c r="S3" s="5">
-        <x:v>46065</x:v>
+        <x:v>46171</x:v>
       </x:c>
       <x:c r="T3" s="0">
-        <x:v>6575</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="V3" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:22">
-      <x:c r="A4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I4" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J4" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K4" s="0">
-        <x:v>228.51</x:v>
-      </x:c>
-      <x:c r="L4" s="0">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="M4" s="0" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="P4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="R4" s="5">
-        <x:v>761475</x:v>
-      </x:c>
-      <x:c r="S4" s="5">
-        <x:v>768785</x:v>
-      </x:c>
-      <x:c r="T4" s="0">
-        <x:v>7310</x:v>
-      </x:c>
-      <x:c r="U4" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="V4" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
